--- a/outputs/deliverables/requirement_3_physical_testing/test_cases/test_cases.xlsx
+++ b/outputs/deliverables/requirement_3_physical_testing/test_cases/test_cases.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status" sheetId="1" r:id="Rc3f49caafcf74bba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="test_cases" sheetId="2" r:id="Rf5153d36bec94701"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="3" r:id="Rbfd7c07b6c2648d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="traceability" sheetId="4" r:id="R0678ffa4a1c1434a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="review" sheetId="5" r:id="R89b01e4c2a004b0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="candidate_test_cases" sheetId="6" r:id="R4a1e1472282b4673"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status" sheetId="1" r:id="R4c634814cff64f0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="test_cases" sheetId="2" r:id="R039a3f46e72f4e88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="3" r:id="R7efed876f2044f99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="traceability" sheetId="4" r:id="Rdd4bcd1647204735"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="review" sheetId="5" r:id="R67a8a5ea72d94d74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="candidate_test_cases" sheetId="6" r:id="Red7153c00c4f4dd7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -360,7 +360,7 @@
         <x:v>Source template</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>inputs/testcase-templates/testcase-template.xls</x:v>
+        <x:v>instructor-provided testcase-template.xls</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
